--- a/administrative_forms/009_email_notification_settings--administrative_forms.xlsx
+++ b/administrative_forms/009_email_notification_settings--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>notification_frequency</t>
+          <t>How often do you want to receive emails?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>notification_type</t>
+          <t>email_type</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>email_format</t>
+          <t>Email format</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cc_email</t>
+          <t>CC email address</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bcc_email</t>
+          <t>BCC email address</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>send_to</t>
+          <t>Email recipient</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>send_from</t>
+          <t>Email sender</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>send_to_email</t>
+          <t>Email recipient's email</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>send_cc_email</t>
+          <t>Send Cc Email</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>subject</t>
+          <t>Email subject</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,287 +778,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>email_body</t>
+          <t>Email body</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>reply_to</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>reply_to</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>send_to</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>send_to</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>reply_to</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>reply_to</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>send_from</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>send_from</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>send_from</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>send_from</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>send_from</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>send_from</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>send_from</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>send_from</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>send_from</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>send_from</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>send_to</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>send_to</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>send_to</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>send_to</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>send_to</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>send_to</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>reply_to</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>reply_to</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1075,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1125,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1142,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1159,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'send_updates'}</t>
+          <t>send_updates</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Send updates'}</t>
+          <t>Send updates</t>
         </is>
       </c>
     </row>
@@ -1176,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'send_reminders'}</t>
+          <t>send_reminders</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Send reminders'}</t>
+          <t>Send reminders</t>
         </is>
       </c>
     </row>
@@ -1193,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'plain_text'}</t>
+          <t>plain_text</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Plain text'}</t>
+          <t>Plain text</t>
         </is>
       </c>
     </row>
@@ -1210,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'html_format'}</t>
+          <t>html_format</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'HTML format'}</t>
+          <t>HTML format</t>
         </is>
       </c>
     </row>
@@ -1227,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'admin'}</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Admin'}</t>
+          <t>Admin</t>
         </is>
       </c>
     </row>
@@ -1244,182 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Staff'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>send_to_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'admin'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Admin'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>send_to_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'staff'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Staff'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>reply_to_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'admin'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Admin'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>reply_to_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'staff'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Staff'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>send_to_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'admin'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Admin'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>send_to_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'staff'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Staff'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>send_to_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'admin'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Admin'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>send_to_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'staff'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Staff'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>send_to_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'admin'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Admin'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>send_to_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'staff'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Staff'}</t>
+          <t>Staff</t>
         </is>
       </c>
     </row>
